--- a/data/trans_camb/IP7_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP7_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,0</t>
+          <t>-2,7; 4,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,1</t>
+          <t>-2,87; 4,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,22</t>
+          <t>-2,66; 4,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,94</t>
+          <t>-4,17; 0,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,76</t>
+          <t>-3,41; 2,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,36</t>
+          <t>-2,63; 4,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,61</t>
+          <t>-2,67; 1,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,05</t>
+          <t>-2,31; 2,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,8</t>
+          <t>-2,01; 2,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 466,2</t>
+          <t>-76,03; 432,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,75; 502,71</t>
+          <t>-82,81; 448,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,35; 623,07</t>
+          <t>-78,59; 442,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 175,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 347,78</t>
+          <t>-85,2; 239,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,57; 458,09</t>
+          <t>-74,64; 421,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 109,36</t>
+          <t>-72,08; 116,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 141,39</t>
+          <t>-67,32; 150,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,28; 190,83</t>
+          <t>-59,27; 166,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,96</t>
+          <t>-3,25; 1,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,85</t>
+          <t>-2,49; 1,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 15,47</t>
+          <t>-0,24; 15,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -1,86</t>
+          <t>-7,68; -1,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -0,91</t>
+          <t>-7,09; -1,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,96</t>
+          <t>-6,81; -0,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; -0,96</t>
+          <t>-4,59; -1,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; -0,38</t>
+          <t>-4,01; -0,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,68</t>
+          <t>-2,75; 4,1</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-88,51; 110,56</t>
+          <t>-88,46; 196,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 188,58</t>
+          <t>-76,81; 187,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 1443,13</t>
+          <t>-30,34; 1127,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-90,54; -29,81</t>
+          <t>-92,19; -28,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,85; -9,77</t>
+          <t>-87,88; -12,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,08; -15,93</t>
+          <t>-83,37; -13,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-86,24; -27,62</t>
+          <t>-85,49; -29,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,08; -7,74</t>
+          <t>-75,24; -1,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,36; 115,48</t>
+          <t>-58,84; 122,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,16</t>
+          <t>-1,19; 4,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,69</t>
+          <t>-1,96; 2,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,49</t>
+          <t>-2,02; 3,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,54</t>
+          <t>-1,36; 5,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 4,2</t>
+          <t>-1,66; 3,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,94</t>
+          <t>-3,39; 1,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,51</t>
+          <t>-0,4; 3,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,55</t>
+          <t>-1,14; 2,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,67</t>
+          <t>-2,1; 1,79</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 770,14</t>
+          <t>-59,97; 780,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,45; 555,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,86; 502,62</t>
+          <t>-77,06; 480,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 498,43</t>
+          <t>-45,34; 568,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 470,13</t>
+          <t>-61,94; 392,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 358,43</t>
+          <t>-100,0; 215,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 325,15</t>
+          <t>-17,37; 349,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 223,07</t>
+          <t>-45,04; 213,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,18; 161,77</t>
+          <t>-63,98; 161,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,09</t>
+          <t>-0,08; 4,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,05</t>
+          <t>-1,08; 2,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,06</t>
+          <t>-0,98; 2,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,63</t>
+          <t>-2,16; 3,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,68</t>
+          <t>-3,81; 0,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,29</t>
+          <t>-2,04; 4,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,1</t>
+          <t>-0,62; 3,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,69</t>
+          <t>-1,88; 0,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,78</t>
+          <t>-1,01; 2,71</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,08; —</t>
+          <t>-47,82; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 221,5</t>
+          <t>-55,44; 253,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,87; 77,72</t>
+          <t>-88,03; 118,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 311,5</t>
+          <t>-56,42; 261,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 281,6</t>
+          <t>-25,79; 275,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,22; 78,34</t>
+          <t>-78,21; 108,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-37,94; 272,83</t>
+          <t>-43,74; 234,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,83</t>
+          <t>-0,54; 1,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,34</t>
+          <t>-1,0; 1,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,36</t>
+          <t>-0,11; 4,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,41</t>
+          <t>-2,48; 0,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; -0,04</t>
+          <t>-2,86; -0,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,46</t>
+          <t>-2,52; 0,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,68</t>
+          <t>-1,18; 0,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,25</t>
+          <t>-1,58; 0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,68</t>
+          <t>-0,93; 1,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 162,32</t>
+          <t>-27,26; 157,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 117,53</t>
+          <t>-44,5; 113,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 350,64</t>
+          <t>-11,13; 340,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 14,7</t>
+          <t>-57,91; 15,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 3,64</t>
+          <t>-66,7; -0,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 20,14</t>
+          <t>-58,11; 20,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 31,75</t>
+          <t>-36,41; 35,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 13,67</t>
+          <t>-48,32; 9,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 74,12</t>
+          <t>-31,55; 76,54</t>
         </is>
       </c>
     </row>
